--- a/data/trans_dic/P1403-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1403-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,9; 14,12</t>
+          <t>8,42; 14,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,67; 20,25</t>
+          <t>12,55; 19,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,3; 17,01</t>
+          <t>10,28; 17,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17,71; 24,36</t>
+          <t>17,69; 24,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,72; 13,34</t>
+          <t>6,83; 13,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,29; 13,83</t>
+          <t>6,32; 13,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,67; 12,99</t>
+          <t>5,77; 12,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,08; 14,97</t>
+          <t>10,48; 15,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,4; 12,55</t>
+          <t>8,53; 12,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,79; 16,37</t>
+          <t>10,63; 15,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,92; 13,93</t>
+          <t>9,04; 13,76</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,85; 18,94</t>
+          <t>14,99; 19,29</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,15; 15,78</t>
+          <t>9,32; 16,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,75; 16,35</t>
+          <t>9,71; 16,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,19; 18,77</t>
+          <t>11,38; 18,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,76; 24,7</t>
+          <t>18,08; 25,1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,36; 8,31</t>
+          <t>3,25; 8,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,78; 13,97</t>
+          <t>6,5; 13,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,57; 12,03</t>
+          <t>5,73; 12,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,51; 15,41</t>
+          <t>11,26; 16,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,75; 10,99</t>
+          <t>6,71; 11,1</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,0; 13,87</t>
+          <t>9,17; 14,16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,47; 14,29</t>
+          <t>9,33; 14,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,4; 19,67</t>
+          <t>15,73; 20,21</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>21,79%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10,55; 16,43</t>
+          <t>10,42; 16,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,1; 25,26</t>
+          <t>18,28; 25,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,35; 19,64</t>
+          <t>13,43; 19,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,2; 22,57</t>
+          <t>17,76; 24,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,88; 18,57</t>
+          <t>7,87; 18,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,74; 27,43</t>
+          <t>17,17; 27,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,44; 28,59</t>
+          <t>14,09; 27,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>20,03; 30,22</t>
+          <t>19,28; 28,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,74; 15,93</t>
+          <t>10,56; 15,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,79; 24,54</t>
+          <t>19,03; 24,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,46; 20,4</t>
+          <t>14,65; 20,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,06; 22,89</t>
+          <t>19,15; 24,91</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>18,64%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,1; 19,19</t>
+          <t>14,92; 19,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,02; 21,78</t>
+          <t>16,71; 21,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,36; 20,85</t>
+          <t>16,05; 20,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,12; 23,93</t>
+          <t>18,77; 23,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,02; 17,03</t>
+          <t>11,71; 16,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,59; 13,27</t>
+          <t>8,38; 13,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,13; 13,58</t>
+          <t>9,05; 13,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,16; 65,57</t>
+          <t>13,59; 17,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,49; 17,66</t>
+          <t>14,51; 17,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,15; 17,62</t>
+          <t>14,28; 17,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13,85; 17,09</t>
+          <t>13,96; 17,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,32; 48,28</t>
+          <t>17,08; 20,05</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,08; 16,08</t>
+          <t>9,38; 16,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,1; 22,12</t>
+          <t>14,98; 21,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,62; 19,6</t>
+          <t>13,65; 19,63</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,15; 24,38</t>
+          <t>15,84; 22,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,6; 19,0</t>
+          <t>12,65; 19,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,17; 28,81</t>
+          <t>22,4; 28,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,32; 22,11</t>
+          <t>16,23; 22,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,39; 30,03</t>
+          <t>25,35; 30,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>12,11; 16,95</t>
+          <t>12,25; 16,9</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20,22; 25,1</t>
+          <t>20,31; 25,12</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15,78; 20,07</t>
+          <t>15,89; 19,91</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,21; 26,28</t>
+          <t>22,3; 25,99</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,72%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,5</t>
+          <t>0,58; 3,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,49</t>
+          <t>0,37; 3,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,79; 4,07</t>
+          <t>0,78; 4,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>22,71; 27,41</t>
+          <t>22,78; 27,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,79; 34,52</t>
+          <t>28,74; 34,1</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,3; 30,42</t>
+          <t>24,55; 30,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26,96; 32,23</t>
+          <t>26,05; 31,44</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18,34; 22,51</t>
+          <t>18,42; 22,51</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>23,25; 27,95</t>
+          <t>23,05; 27,8</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>19,37; 24,39</t>
+          <t>19,41; 24,37</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20,71; 25,24</t>
+          <t>20,76; 24,87</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>11,91; 14,25</t>
+          <t>11,87; 14,26</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,59; 18,28</t>
+          <t>15,6; 18,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,02; 16,49</t>
+          <t>13,88; 16,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,88; 20,13</t>
+          <t>18,13; 20,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,73; 18,41</t>
+          <t>15,54; 18,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,71; 22,42</t>
+          <t>19,47; 22,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,29; 18,95</t>
+          <t>16,48; 19,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>20,43; 41,52</t>
+          <t>20,09; 22,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,15; 15,86</t>
+          <t>14,13; 15,97</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17,96; 19,87</t>
+          <t>18,0; 19,96</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,52; 17,34</t>
+          <t>15,59; 17,42</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,98; 30,93</t>
+          <t>19,5; 21,1</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>106158</t>
+          <t>114897</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>54841</t>
+          <t>62982</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>160999</t>
+          <t>177879</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>37442; 66879</t>
+          <t>39915; 66863</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>55406; 88537</t>
+          <t>54891; 85798</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44189; 72981</t>
+          <t>44114; 74078</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>89270; 122761</t>
+          <t>97013; 133701</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20601; 40900</t>
+          <t>20944; 40828</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19766; 43503</t>
+          <t>19859; 43644</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19688; 45100</t>
+          <t>20026; 45071</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>45097; 66965</t>
+          <t>51205; 76244</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>65560; 97968</t>
+          <t>66563; 98923</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81068; 123057</t>
+          <t>79918; 119811</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>69251; 108116</t>
+          <t>70135; 106769</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>141330; 180242</t>
+          <t>155371; 200001</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>95786</t>
+          <t>103506</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>49080</t>
+          <t>58007</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>144866</t>
+          <t>161513</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33581; 57902</t>
+          <t>34209; 59629</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40823; 68493</t>
+          <t>40650; 67968</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42211; 70823</t>
+          <t>42924; 71055</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80314; 111707</t>
+          <t>87381; 121280</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12502; 30906</t>
+          <t>12078; 30825</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22913; 47226</t>
+          <t>21960; 46330</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20730; 44780</t>
+          <t>21324; 45112</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>40060; 58758</t>
+          <t>47524; 69798</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49864; 81191</t>
+          <t>49538; 82009</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68086; 104970</t>
+          <t>69418; 107135</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70980; 107119</t>
+          <t>69937; 106855</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>128325; 163953</t>
+          <t>142335; 182904</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89357</t>
+          <t>98239</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40572</t>
+          <t>45076</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>129929</t>
+          <t>143316</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>57248; 89131</t>
+          <t>56516; 87498</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>113947; 158980</t>
+          <t>115045; 158445</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69664; 102520</t>
+          <t>70073; 102368</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34727; 150664</t>
+          <t>83626; 116841</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13215; 31150</t>
+          <t>13202; 31178</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43541; 71353</t>
+          <t>44664; 72364</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23987; 47490</t>
+          <t>23403; 46156</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>33315; 50258</t>
+          <t>36020; 53809</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>76277; 113159</t>
+          <t>75014; 111639</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>167139; 218259</t>
+          <t>169294; 219952</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>99501; 140361</t>
+          <t>100781; 142036</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50523; 190835</t>
+          <t>125947; 163788</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>219547</t>
+          <t>237354</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>326806</t>
+          <t>133723</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>546353</t>
+          <t>371077</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>186972; 237691</t>
+          <t>184737; 238633</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>197219; 252431</t>
+          <t>193632; 252867</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>188107; 239645</t>
+          <t>184493; 237622</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>197569; 247329</t>
+          <t>212144; 266126</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>85828; 121640</t>
+          <t>83674; 120120</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>65654; 101502</t>
+          <t>64061; 100867</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>75375; 112123</t>
+          <t>74705; 113124</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>148163; 640961</t>
+          <t>116945; 150686</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>282881; 344846</t>
+          <t>283259; 345430</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>272153; 339053</t>
+          <t>274686; 336608</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>273603; 337680</t>
+          <t>275860; 339675</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>368473; 970991</t>
+          <t>340002; 399192</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>98128</t>
+          <t>106797</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>215293</t>
+          <t>230403</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>313421</t>
+          <t>337200</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>31832; 56382</t>
+          <t>32892; 57055</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>77116; 112950</t>
+          <t>76512; 112170</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>84552; 121658</t>
+          <t>84756; 121862</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>81298; 115588</t>
+          <t>89796; 125405</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>71637; 108073</t>
+          <t>71975; 108060</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>168521; 219038</t>
+          <t>170284; 216567</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>120501; 163201</t>
+          <t>119829; 163889</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>162609; 251813</t>
+          <t>210311; 250838</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>111310; 155790</t>
+          <t>112629; 155363</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>257012; 318948</t>
+          <t>258045; 319180</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>214479; 272771</t>
+          <t>215931; 270546</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>252164; 344869</t>
+          <t>311464; 362965</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>224993</t>
+          <t>240986</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>229484</t>
+          <t>245474</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1769; 10432</t>
+          <t>1743; 10999</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1010; 9303</t>
+          <t>993; 9939</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 7355</t>
+          <t>0; 7700</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1895; 9781</t>
+          <t>1839; 9934</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>283609; 342223</t>
+          <t>284427; 344683</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>319107; 382606</t>
+          <t>318556; 377938</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>262887; 329186</t>
+          <t>265656; 329969</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>204980; 245021</t>
+          <t>219654; 265124</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>283742; 348249</t>
+          <t>284929; 348191</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>319752; 384316</t>
+          <t>316922; 382335</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>265148; 333914</t>
+          <t>265802; 333690</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>207297; 252649</t>
+          <t>224280; 268659</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>613467</t>
+          <t>665280</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>911586</t>
+          <t>771178</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1525053</t>
+          <t>1436458</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>389336; 465962</t>
+          <t>388085; 466267</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>533306; 625679</t>
+          <t>533853; 628754</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>474831; 558219</t>
+          <t>469882; 557918</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>468011; 678813</t>
+          <t>622977; 710247</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>531370; 621870</t>
+          <t>525019; 615678</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>698838; 795089</t>
+          <t>690468; 792654</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>575339; 669301</t>
+          <t>581907; 685309</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>729688; 1482699</t>
+          <t>729195; 812205</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>940964; 1054398</t>
+          <t>939538; 1061532</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1251188; 1384400</t>
+          <t>1253848; 1390862</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1073340; 1199303</t>
+          <t>1078587; 1204819</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1318106; 2147635</t>
+          <t>1378074; 1491308</t>
         </is>
       </c>
     </row>
